--- a/doc/4-10#五菱/点位信息.xlsx
+++ b/doc/4-10#五菱/点位信息.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Sheet1" sheetId="5" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$Q$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$Q$34</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="63">
   <si>
     <t>设备编号</t>
   </si>
@@ -200,6 +200,9 @@
   </si>
   <si>
     <t>间隙</t>
+  </si>
+  <si>
+    <t>下发游隙SN</t>
   </si>
   <si>
     <t>四分厂4-10-震动</t>
@@ -1207,7 +1210,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="11.125" customWidth="1"/>
@@ -1353,13 +1356,13 @@
         <v>20</v>
       </c>
       <c r="I4" s="2">
-        <v>1524</v>
+        <v>1700</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>21</v>
       </c>
       <c r="K4" s="2">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="L4" s="2"/>
     </row>
@@ -1449,13 +1452,13 @@
         <v>20</v>
       </c>
       <c r="I7" s="2">
-        <v>1570</v>
+        <v>1740</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>21</v>
       </c>
       <c r="K7" s="2">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="L7" s="2"/>
     </row>
@@ -1545,13 +1548,13 @@
         <v>20</v>
       </c>
       <c r="I10" s="2">
-        <v>1724</v>
+        <v>2100</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>21</v>
       </c>
       <c r="K10" s="2">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="L10" s="2"/>
     </row>
@@ -1743,13 +1746,13 @@
         <v>20</v>
       </c>
       <c r="I16" s="2">
-        <v>1764</v>
+        <v>2140</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>21</v>
       </c>
       <c r="K16" s="2">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="L16" s="2"/>
     </row>
@@ -1839,13 +1842,13 @@
         <v>20</v>
       </c>
       <c r="I19" s="2">
-        <v>1864</v>
+        <v>2100</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>21</v>
       </c>
       <c r="K19" s="2">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="L19" s="2"/>
     </row>
@@ -1935,13 +1938,13 @@
         <v>20</v>
       </c>
       <c r="I22" s="2">
-        <v>1884</v>
+        <v>2220</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>21</v>
       </c>
       <c r="K22" s="2">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="L22" s="2"/>
     </row>
@@ -2137,7 +2140,7 @@
       </c>
       <c r="L28" s="2"/>
     </row>
-    <row r="29" ht="14.25" spans="1:12">
+    <row r="29" spans="1:12">
       <c r="A29" s="5" t="s">
         <v>39</v>
       </c>
@@ -2171,55 +2174,54 @@
     </row>
     <row r="30" ht="14.25" spans="1:12">
       <c r="A30" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D30" s="2">
+        <v>4005</v>
+      </c>
+      <c r="F30" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C30" t="s">
-        <v>56</v>
-      </c>
-      <c r="D30" s="2">
-        <v>9000</v>
-      </c>
-      <c r="F30" t="s">
-        <v>57</v>
-      </c>
-      <c r="H30" t="s">
-        <v>58</v>
+      <c r="H30" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="I30" s="2">
-        <v>10</v>
-      </c>
-      <c r="J30" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="K30" s="6">
-        <v>1</v>
+        <v>1804</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K30" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="31" ht="14.25" spans="1:12">
       <c r="A31" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C31" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D31" s="2">
         <v>9000</v>
       </c>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2" t="s">
+      <c r="F31" t="s">
+        <v>58</v>
+      </c>
+      <c r="H31" t="s">
         <v>59</v>
       </c>
-      <c r="H31" t="s">
-        <v>16</v>
-      </c>
       <c r="I31" s="2">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="J31" s="6" t="s">
         <v>17</v>
@@ -2228,15 +2230,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:12">
+    <row r="32" ht="14.25" spans="1:12">
       <c r="A32" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C32" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D32" s="2">
         <v>9000</v>
@@ -2245,28 +2247,28 @@
       <c r="F32" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="H32" s="2" t="s">
-        <v>20</v>
+      <c r="H32" t="s">
+        <v>16</v>
       </c>
       <c r="I32" s="2">
-        <v>1920</v>
-      </c>
-      <c r="J32" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K32" s="2">
-        <v>40</v>
+        <v>50</v>
+      </c>
+      <c r="J32" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="K32" s="6">
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:11">
       <c r="A33" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C33" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D33" s="2">
         <v>9000</v>
@@ -2279,27 +2281,60 @@
         <v>20</v>
       </c>
       <c r="I33" s="2">
-        <v>1900</v>
+        <v>2100</v>
       </c>
       <c r="J33" s="2" t="s">
         <v>21</v>
       </c>
       <c r="K33" s="2">
-        <v>40</v>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C34" t="s">
+        <v>57</v>
+      </c>
+      <c r="D34" s="2">
+        <v>9000</v>
+      </c>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I34" s="2">
+        <v>1900</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K34" s="2">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:Q33" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:Q34" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
-  <conditionalFormatting sqref="F33">
+  <conditionalFormatting sqref="F30">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5:F7">
+  <conditionalFormatting sqref="F34">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F4 F8:F32 F34:F1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+  <conditionalFormatting sqref="F5:F7">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F1:F4 F8:F29 F31:F33 F35:F1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
